--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-29.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-29.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_2B593D9757A9EF266B382611593F087673EFFF94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8073D7F0-899F-4B77-8196-87AE5457DD2B}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_2B593D9757A9EF266B382611593F087673EFFF94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E88DD0C2-C562-47C8-B75F-73C5F9C7F485}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,6 +225,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -778,13 +782,13 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <v>RED</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
